--- a/diseases/d142/2015-2019.xlsx
+++ b/diseases/d142/2015-2019.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>118</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>2.153395681437957</v>
       </c>
@@ -2049,9 +2046,6 @@
       <c r="O10" t="n">
         <v>255</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>4.653524565819314</v>
       </c>
@@ -3185,9 +3179,6 @@
       <c r="O17" t="n">
         <v>352</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>6.423688812425093</v>
       </c>
@@ -4321,9 +4312,6 @@
       <c r="O24" t="n">
         <v>334</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>6.095204725426083</v>
       </c>
@@ -5457,9 +5445,6 @@
       <c r="O31" t="n">
         <v>247</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>4.507531638264199</v>
       </c>
@@ -6741,9 +6726,6 @@
       <c r="O39" t="n">
         <v>109</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>1.989153637938452</v>
       </c>
@@ -7877,9 +7859,6 @@
       <c r="O46" t="n">
         <v>24</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.4379787826653473</v>
       </c>
@@ -9013,9 +8992,6 @@
       <c r="O53" t="n">
         <v>30</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.5474734783316841</v>
       </c>
@@ -10297,9 +10273,6 @@
       <c r="O61" t="n">
         <v>17</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.3102349710546209</v>
       </c>
@@ -11433,9 +11406,6 @@
       <c r="O68" t="n">
         <v>36</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0.6569681739980209</v>
       </c>
@@ -12717,9 +12687,6 @@
       <c r="O76" t="n">
         <v>141</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>2.573125348158915</v>
       </c>
@@ -13853,9 +13820,6 @@
       <c r="O83" t="n">
         <v>772</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>14.08831750906867</v>
       </c>
@@ -14989,9 +14953,6 @@
       <c r="O90" t="n">
         <v>1559</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>28.36882529953313</v>
       </c>
@@ -16504,9 +16465,6 @@
       <c r="O99" t="n">
         <v>1977</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>35.97509147990827</v>
       </c>
@@ -17871,9 +17829,6 @@
       <c r="O107" t="n">
         <v>879</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>15.99499514964055</v>
       </c>
@@ -19238,9 +19193,6 @@
       <c r="O115" t="n">
         <v>258</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>4.694776733341595</v>
       </c>
@@ -20753,9 +20705,6 @@
       <c r="O124" t="n">
         <v>51</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.9280372612419431</v>
       </c>
@@ -22120,9 +22069,6 @@
       <c r="O132" t="n">
         <v>13</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.2365585175714757</v>
       </c>
@@ -23487,9 +23433,6 @@
       <c r="O140" t="n">
         <v>5</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.09098404521979835</v>
       </c>
@@ -25002,9 +24945,6 @@
       <c r="O149" t="n">
         <v>9</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.163771281395637</v>
       </c>
@@ -26369,9 +26309,6 @@
       <c r="O157" t="n">
         <v>5</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.09098404521979835</v>
       </c>
@@ -27505,9 +27442,6 @@
       <c r="O164" t="n">
         <v>16</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.2911489447033547</v>
       </c>
@@ -28789,9 +28723,6 @@
       <c r="O172" t="n">
         <v>43</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.7824627888902659</v>
       </c>
@@ -30156,9 +30087,6 @@
       <c r="O180" t="n">
         <v>132</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>2.401978793802676</v>
       </c>
@@ -31671,9 +31599,6 @@
       <c r="O189" t="n">
         <v>230</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>4.175444176489853</v>
       </c>
@@ -33038,9 +32963,6 @@
       <c r="O197" t="n">
         <v>404</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>7.334258466530002</v>
       </c>
@@ -34405,9 +34327,6 @@
       <c r="O205" t="n">
         <v>573</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>10.40230223099429</v>
       </c>
@@ -35772,9 +35691,6 @@
       <c r="O213" t="n">
         <v>437</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>7.93334393533072</v>
       </c>
@@ -37287,9 +37203,6 @@
       <c r="O222" t="n">
         <v>323</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>5.863775952200967</v>
       </c>
@@ -38654,9 +38567,6 @@
       <c r="O230" t="n">
         <v>121</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>2.196646718935966</v>
       </c>
@@ -40021,9 +39931,6 @@
       <c r="O238" t="n">
         <v>34</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.6172395739158913</v>
       </c>
@@ -41536,9 +41443,6 @@
       <c r="O247" t="n">
         <v>19</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.3449279971882922</v>
       </c>
@@ -42903,9 +42807,6 @@
       <c r="O255" t="n">
         <v>23</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.4175444176489853</v>
       </c>
@@ -44418,9 +44319,6 @@
       <c r="O264" t="n">
         <v>59</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>1.071092201795223</v>
       </c>
@@ -45785,9 +45683,6 @@
       <c r="O272" t="n">
         <v>219</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>3.975749020222947</v>
       </c>
@@ -47152,9 +47047,6 @@
       <c r="O280" t="n">
         <v>1403</v>
       </c>
-      <c r="Q280" t="n">
-        <v>0</v>
-      </c>
       <c r="R280" t="n">
         <v>25.4702094765881</v>
       </c>
@@ -48667,9 +48559,6 @@
       <c r="O289" t="n">
         <v>2549</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>46.21323009175656</v>
       </c>
@@ -50034,9 +49923,6 @@
       <c r="O297" t="n">
         <v>2633</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>47.73614548120636</v>
       </c>
@@ -51401,9 +51287,6 @@
       <c r="O305" t="n">
         <v>1853</v>
       </c>
-      <c r="Q305" t="n">
-        <v>0</v>
-      </c>
       <c r="R305" t="n">
         <v>33.59478829345818</v>
       </c>
@@ -52916,9 +52799,6 @@
       <c r="O314" t="n">
         <v>620</v>
       </c>
-      <c r="Q314" t="n">
-        <v>0</v>
-      </c>
       <c r="R314" t="n">
         <v>11.24056596974856</v>
       </c>
@@ -54283,9 +54163,6 @@
       <c r="O322" t="n">
         <v>140</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>2.538192315749674</v>
       </c>
@@ -55650,9 +55527,6 @@
       <c r="O330" t="n">
         <v>22</v>
       </c>
-      <c r="Q330" t="n">
-        <v>0</v>
-      </c>
       <c r="R330" t="n">
         <v>0.3988587924749487</v>
       </c>
@@ -57165,9 +57039,6 @@
       <c r="O339" t="n">
         <v>7</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0.1269096157874837</v>
       </c>
@@ -58532,9 +58403,6 @@
       <c r="O347" t="n">
         <v>7</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0.1269096157874837</v>
       </c>
@@ -59899,9 +59767,6 @@
       <c r="O355" t="n">
         <v>16</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0.2900791217999627</v>
       </c>
@@ -61414,9 +61279,6 @@
       <c r="O364" t="n">
         <v>11</v>
       </c>
-      <c r="Q364" t="n">
-        <v>0</v>
-      </c>
       <c r="R364" t="n">
         <v>0.1994293962374744</v>
       </c>
@@ -62781,9 +62643,6 @@
       <c r="O372" t="n">
         <v>24</v>
       </c>
-      <c r="Q372" t="n">
-        <v>0</v>
-      </c>
       <c r="R372" t="n">
         <v>0.4351186826999441</v>
       </c>
@@ -64148,9 +64007,6 @@
       <c r="O380" t="n">
         <v>124</v>
       </c>
-      <c r="Q380" t="n">
-        <v>0</v>
-      </c>
       <c r="R380" t="n">
         <v>2.248113193949711</v>
       </c>
@@ -65663,9 +65519,6 @@
       <c r="O389" t="n">
         <v>305</v>
       </c>
-      <c r="Q389" t="n">
-        <v>0</v>
-      </c>
       <c r="R389" t="n">
         <v>5.523602170974865</v>
       </c>
@@ -67030,9 +66883,6 @@
       <c r="O397" t="n">
         <v>673</v>
       </c>
-      <c r="Q397" t="n">
-        <v>0</v>
-      </c>
       <c r="R397" t="n">
         <v>12.18814511824946</v>
       </c>
@@ -68397,9 +68247,6 @@
       <c r="O405" t="n">
         <v>814</v>
       </c>
-      <c r="Q405" t="n">
-        <v>0</v>
-      </c>
       <c r="R405" t="n">
         <v>14.74167923663456</v>
       </c>
@@ -69912,9 +69759,6 @@
       <c r="O414" t="n">
         <v>820</v>
       </c>
-      <c r="Q414" t="n">
-        <v>0</v>
-      </c>
       <c r="R414" t="n">
         <v>14.85034026294882</v>
       </c>
@@ -71279,9 +71123,6 @@
       <c r="O422" t="n">
         <v>402</v>
       </c>
-      <c r="Q422" t="n">
-        <v>0</v>
-      </c>
       <c r="R422" t="n">
         <v>7.280288763055396</v>
       </c>
@@ -72646,9 +72487,6 @@
       <c r="O430" t="n">
         <v>125</v>
       </c>
-      <c r="Q430" t="n">
-        <v>0</v>
-      </c>
       <c r="R430" t="n">
         <v>2.263771381547076</v>
       </c>
@@ -74161,9 +73999,6 @@
       <c r="O439" t="n">
         <v>30</v>
       </c>
-      <c r="Q439" t="n">
-        <v>0</v>
-      </c>
       <c r="R439" t="n">
         <v>0.5433051315712982</v>
       </c>
@@ -75528,9 +75363,6 @@
       <c r="O447" t="n">
         <v>11</v>
       </c>
-      <c r="Q447" t="n">
-        <v>0</v>
-      </c>
       <c r="R447" t="n">
         <v>0.1992118815761427</v>
       </c>
@@ -77043,9 +76875,6 @@
       <c r="O456" t="n">
         <v>8</v>
       </c>
-      <c r="Q456" t="n">
-        <v>0</v>
-      </c>
       <c r="R456" t="n">
         <v>0.1448813684190129</v>
       </c>
@@ -78410,9 +78239,6 @@
       <c r="O464" t="n">
         <v>38</v>
       </c>
-      <c r="Q464" t="n">
-        <v>0</v>
-      </c>
       <c r="R464" t="n">
         <v>0.6881864999903111</v>
       </c>
@@ -79777,9 +79603,6 @@
       <c r="O472" t="n">
         <v>205</v>
       </c>
-      <c r="Q472" t="n">
-        <v>0</v>
-      </c>
       <c r="R472" t="n">
         <v>3.712585065737204</v>
       </c>
@@ -81291,9 +81114,6 @@
       </c>
       <c r="O481" t="n">
         <v>953</v>
-      </c>
-      <c r="Q481" t="n">
-        <v>0</v>
       </c>
       <c r="R481" t="n">
         <v>17.25899301291491</v>
